--- a/results/feature_selection/global_ind/wrapper/P/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wrapper/P/metrics_global.xlsx
@@ -488,274 +488,274 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, Plag1, X_calc, V_calc</t>
+          <t>t, t_ind, t_ind_ad, T, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9290897099738711</v>
+        <v>0.8436387869686192</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0937592941857292</v>
+        <v>0.109243679303767</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01647288977720174</v>
+        <v>0.03632365664766563</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1283467560057586</v>
+        <v>0.190587661320626</v>
       </c>
       <c r="H2" t="n">
-        <v>32.02491959920357</v>
+        <v>27.50674258807508</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0358041098518799</v>
+        <v>0.07833492356278021</v>
       </c>
       <c r="J2" t="n">
-        <v>-209.7261218305521</v>
+        <v>-155.0254467913487</v>
       </c>
       <c r="K2" t="n">
-        <v>-197.7922175511665</v>
+        <v>-131.1576382325774</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plag1, X_calc, V_calc</t>
+          <t>t_ind, t_ind_ad, I, FS_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9149976032859465</v>
+        <v>0.8344014981609486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09668322859093942</v>
+        <v>0.1255424591291691</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01974657149692409</v>
+        <v>0.03846953477498492</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1405224946295933</v>
+        <v>0.1961365207578255</v>
       </c>
       <c r="H3" t="n">
-        <v>25.06882464979346</v>
+        <v>32.98985015697989</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04082331906206293</v>
+        <v>0.07960822489420488</v>
       </c>
       <c r="J3" t="n">
-        <v>-205.9378714810288</v>
+        <v>-163.9259873959711</v>
       </c>
       <c r="K3" t="n">
-        <v>-199.9709193413359</v>
+        <v>-151.9920831165855</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>I, Plag1</t>
+          <t>t, t_ind, t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8895375855377852</v>
+        <v>0.7254227145484026</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08552578262644228</v>
+        <v>0.1682165101220789</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02566108779542636</v>
+        <v>0.06378596613976285</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1601907856133628</v>
+        <v>0.252558836986083</v>
       </c>
       <c r="H4" t="n">
-        <v>18.39449190150691</v>
+        <v>45.64842565904668</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05210148579546291</v>
+        <v>0.1290233619333132</v>
       </c>
       <c r="J4" t="n">
-        <v>-193.7900945142747</v>
+        <v>-140.6199922816039</v>
       </c>
       <c r="K4" t="n">
-        <v>-189.8121264211461</v>
+        <v>-132.6640560953468</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t_ind, Plag1</t>
+          <t>t_ind_ad, I, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8760063515604268</v>
+        <v>0.7098572696703398</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1000963055385715</v>
+        <v>0.1735161589770618</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02880447538806514</v>
+        <v>0.06740191324299649</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1697188127110991</v>
+        <v>0.2596187844571276</v>
       </c>
       <c r="H5" t="n">
-        <v>26.22139744854832</v>
+        <v>44.12593441416043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05836122730351756</v>
+        <v>0.1362241583689956</v>
       </c>
       <c r="J5" t="n">
-        <v>-187.550123458672</v>
+        <v>-137.6424212538964</v>
       </c>
       <c r="K5" t="n">
-        <v>-183.5721553655434</v>
+        <v>-129.6864850676393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plag1</t>
+          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8445608550786259</v>
+        <v>0.5889905477305566</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1237376853315673</v>
+        <v>0.2135681384328402</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03610945464203829</v>
+        <v>0.09547998466975401</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1900248790080875</v>
+        <v>0.3089983570664317</v>
       </c>
       <c r="H6" t="n">
-        <v>34.46312563441302</v>
+        <v>63.73060677410766</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07240836172583905</v>
+        <v>0.1956388249496608</v>
       </c>
       <c r="J6" t="n">
-        <v>-177.3448295105676</v>
+        <v>-104.8372864558492</v>
       </c>
       <c r="K6" t="n">
-        <v>-175.3558454640034</v>
+        <v>-82.95846194364219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, FS_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t_ind, t_ind_ad, I</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8344014981609486</v>
+        <v>0.5617703122103209</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1255424591291691</v>
+        <v>0.1639723973001904</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03846953477498492</v>
+        <v>0.1018034102158784</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1961365207578255</v>
+        <v>0.319066466768099</v>
       </c>
       <c r="H7" t="n">
-        <v>32.98985015697989</v>
+        <v>33.23934008273833</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07960822489420488</v>
+        <v>0.2042312934880186</v>
       </c>
       <c r="J7" t="n">
-        <v>-163.9259873959711</v>
+        <v>-117.3744305176696</v>
       </c>
       <c r="K7" t="n">
-        <v>-151.9920831165855</v>
+        <v>-111.4074783779768</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, Xlag1_calc</t>
+          <t>t, t_ind, t_ind_ad, T, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8338261838919017</v>
+        <v>0.3372968735776726</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1452628147031775</v>
+        <v>0.2116835312606389</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03860318376355583</v>
+        <v>0.1539499493309002</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1964769293417317</v>
+        <v>0.3923645617673699</v>
       </c>
       <c r="H8" t="n">
-        <v>42.70537831178454</v>
+        <v>56.99609448956883</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07887437346691858</v>
+        <v>0.3125759024583284</v>
       </c>
       <c r="J8" t="n">
-        <v>-167.7387083495453</v>
+        <v>-77.04089762188816</v>
       </c>
       <c r="K8" t="n">
-        <v>-159.7827721632882</v>
+        <v>-53.17308906311687</v>
       </c>
     </row>
     <row r="9">
@@ -765,36 +765,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>I, Plag1</t>
+          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8328527677103633</v>
+        <v>0.2442608982255661</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1054411889240063</v>
+        <v>0.2243779297866255</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03882931423714318</v>
+        <v>0.1755627697935579</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1970515522322602</v>
+        <v>0.4190021119201643</v>
       </c>
       <c r="H9" t="n">
-        <v>25.34011484422506</v>
+        <v>64.08007139255774</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07832468965289124</v>
+        <v>0.3536156693878207</v>
       </c>
       <c r="J9" t="n">
-        <v>-171.4233089861496</v>
+        <v>-77.94696641856842</v>
       </c>
       <c r="K9" t="n">
-        <v>-167.4453408930211</v>
+        <v>-62.03509404605423</v>
       </c>
     </row>
     <row r="10">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I, Plag1</t>
+          <t>t, t_ind, t_ind_ad, I, V_calc, mu_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8108830663533716</v>
+        <v>0.1963563933310914</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1076170333487985</v>
+        <v>0.2398256863842169</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04393300890202764</v>
+        <v>0.1866912763709153</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2096020250427644</v>
+        <v>0.4320778591537818</v>
       </c>
       <c r="H10" t="n">
-        <v>24.11404763855042</v>
+        <v>66.56304695207569</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08848818632540788</v>
+        <v>0.3752769754603133</v>
       </c>
       <c r="J10" t="n">
-        <v>-164.7548238327819</v>
+        <v>-76.62814356511547</v>
       </c>
       <c r="K10" t="n">
-        <v>-160.7768557396534</v>
+        <v>-62.70525523916555</v>
       </c>
     </row>
     <row r="11">
@@ -843,36 +843,36 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>I, Plag1</t>
+          <t>t_ind_ad, I, V_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7960338123008193</v>
+        <v>0.07647638699522741</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1082712980933705</v>
+        <v>0.2612040064190496</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04738258053953225</v>
+        <v>0.2145401277877305</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2176754017787317</v>
+        <v>0.4631847663597438</v>
       </c>
       <c r="H11" t="n">
-        <v>23.03533833331745</v>
+        <v>80.93337502687031</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09535766268742681</v>
+        <v>0.4287351733528431</v>
       </c>
       <c r="J11" t="n">
-        <v>-160.6730333175388</v>
+        <v>-77.11995803756395</v>
       </c>
       <c r="K11" t="n">
-        <v>-156.6950652244103</v>
+        <v>-71.15300589787113</v>
       </c>
     </row>
     <row r="12">
@@ -882,36 +882,36 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>I, Plag1</t>
+          <t>t_ind_ad, I, FS_calc, mu_calc</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7768107839386732</v>
+        <v>0.07121096798477911</v>
       </c>
       <c r="E12" t="n">
-        <v>0.112242461220708</v>
+        <v>0.2672115545085408</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05184820643496962</v>
+        <v>0.2157633165091127</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2277020123647782</v>
+        <v>0.4645033008592217</v>
       </c>
       <c r="H12" t="n">
-        <v>24.12440895914042</v>
+        <v>79.49461989682045</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1042505093228768</v>
+        <v>0.4316710311609452</v>
       </c>
       <c r="J12" t="n">
-        <v>-155.8094865614438</v>
+        <v>-74.81295436495974</v>
       </c>
       <c r="K12" t="n">
-        <v>-151.8315184683153</v>
+        <v>-66.85701817870265</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wrapper/P/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wrapper/P/metrics_global.xlsx
@@ -492,75 +492,75 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t, t_ind_ad, T, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8436387869686192</v>
+        <v>0.8362849250911507</v>
       </c>
       <c r="E2" t="n">
-        <v>0.109243679303767</v>
+        <v>0.114804682034555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03632365664766563</v>
+        <v>0.0380320032938247</v>
       </c>
       <c r="G2" t="n">
-        <v>0.190587661320626</v>
+        <v>0.1950179563369094</v>
       </c>
       <c r="H2" t="n">
-        <v>27.50674258807508</v>
+        <v>34.18230929465248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07833492356278021</v>
+        <v>0.08123692477833208</v>
       </c>
       <c r="J2" t="n">
-        <v>-155.0254467913487</v>
+        <v>-154.5436732149124</v>
       </c>
       <c r="K2" t="n">
-        <v>-131.1576382325774</v>
+        <v>-132.6648487027054</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, FS_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t_ind_ad, I, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8344014981609486</v>
+        <v>0.7098572696703398</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1255424591291691</v>
+        <v>0.1735161589770618</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03846953477498492</v>
+        <v>0.06740191324299649</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1961365207578255</v>
+        <v>0.2596187844571276</v>
       </c>
       <c r="H3" t="n">
-        <v>32.98985015697989</v>
+        <v>44.12593441416043</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07960822489420488</v>
+        <v>0.1362241583689956</v>
       </c>
       <c r="J3" t="n">
-        <v>-163.9259873959711</v>
+        <v>-137.6424212538964</v>
       </c>
       <c r="K3" t="n">
-        <v>-151.9920831165855</v>
+        <v>-129.6864850676393</v>
       </c>
     </row>
     <row r="4">
@@ -570,42 +570,42 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, V_calc</t>
+          <t>t, t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7254227145484026</v>
+        <v>0.7062294473708337</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1682165101220789</v>
+        <v>0.1967386758059774</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06378596613976285</v>
+        <v>0.06824467833180119</v>
       </c>
       <c r="G4" t="n">
-        <v>0.252558836986083</v>
+        <v>0.2612368242262204</v>
       </c>
       <c r="H4" t="n">
-        <v>45.64842565904668</v>
+        <v>58.46587643650211</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1290233619333132</v>
+        <v>0.1374024406210107</v>
       </c>
       <c r="J4" t="n">
-        <v>-140.6199922816039</v>
+        <v>-138.971414340348</v>
       </c>
       <c r="K4" t="n">
-        <v>-132.6640560953468</v>
+        <v>-133.0044622006551</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -617,223 +617,223 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7098572696703398</v>
+        <v>0.7027391509293971</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1735161589770618</v>
+        <v>0.1743951827832149</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06740191324299649</v>
+        <v>0.06905549533097519</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2596187844571276</v>
+        <v>0.2627841230572638</v>
       </c>
       <c r="H5" t="n">
-        <v>44.12593441416043</v>
+        <v>44.68830522678557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1362241583689956</v>
+        <v>0.1395171014528635</v>
       </c>
       <c r="J5" t="n">
-        <v>-137.6424212538964</v>
+        <v>-136.3336201442326</v>
       </c>
       <c r="K5" t="n">
-        <v>-129.6864850676393</v>
+        <v>-128.3776839579754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5889905477305566</v>
+        <v>0.701780363343072</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2135681384328402</v>
+        <v>0.1868412591201623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09547998466975401</v>
+        <v>0.06927822749330964</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3089983570664317</v>
+        <v>0.2632075749162809</v>
       </c>
       <c r="H6" t="n">
-        <v>63.73060677410766</v>
+        <v>46.17104694945057</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1956388249496608</v>
+        <v>0.1384606502423952</v>
       </c>
       <c r="J6" t="n">
-        <v>-104.8372864558492</v>
+        <v>-142.1597283857503</v>
       </c>
       <c r="K6" t="n">
-        <v>-82.95846194364219</v>
+        <v>-140.170744339186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I</t>
+          <t>t, t_ind_ad, X_calc, V_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5617703122103209</v>
+        <v>0.699094227871854</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1639723973001904</v>
+        <v>0.1561690849903828</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1018034102158784</v>
+        <v>0.06990223302942719</v>
       </c>
       <c r="G7" t="n">
-        <v>0.319066466768099</v>
+        <v>0.264390304340812</v>
       </c>
       <c r="H7" t="n">
-        <v>33.23934008273833</v>
+        <v>37.89696224182769</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2042312934880186</v>
+        <v>0.1412032947590428</v>
       </c>
       <c r="J7" t="n">
-        <v>-117.3744305176696</v>
+        <v>-135.6755149465313</v>
       </c>
       <c r="K7" t="n">
-        <v>-111.4074783779768</v>
+        <v>-127.7195787602741</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t_ind_ad, I, V_calc, mu_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3372968735776726</v>
+        <v>0.200003659553436</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2116835312606389</v>
+        <v>0.2412674038220092</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1539499493309002</v>
+        <v>0.1858439943410907</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3923645617673699</v>
+        <v>0.4310962703864308</v>
       </c>
       <c r="H8" t="n">
-        <v>56.99609448956883</v>
+        <v>69.64390304876264</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3125759024583284</v>
+        <v>0.3725896981727327</v>
       </c>
       <c r="J8" t="n">
-        <v>-77.04089762188816</v>
+        <v>-80.87377565473363</v>
       </c>
       <c r="K8" t="n">
-        <v>-53.17308906311687</v>
+        <v>-70.92885542191226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, mu_calc</t>
+          <t>t_ind_ad, I, V_calc, mu_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2442608982255661</v>
+        <v>0.1994252964473758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2243779297866255</v>
+        <v>0.2413497954684881</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1755627697935579</v>
+        <v>0.1859783515929623</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4190021119201643</v>
+        <v>0.4312520743056922</v>
       </c>
       <c r="H9" t="n">
-        <v>64.08007139255774</v>
+        <v>69.66813686877533</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3536156693878207</v>
+        <v>0.3728572571808609</v>
       </c>
       <c r="J9" t="n">
-        <v>-77.94696641856842</v>
+        <v>-80.83475007170354</v>
       </c>
       <c r="K9" t="n">
-        <v>-62.03509404605423</v>
+        <v>-70.88982983888216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, I, V_calc, mu_calc, Xlag1_calc</t>
+          <t>t_ind_ad, I, X_calc, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1963563933310914</v>
+        <v>0.1900255851338539</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2398256863842169</v>
+        <v>0.2316154062875162</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1866912763709153</v>
+        <v>0.1881619614519561</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4320778591537818</v>
+        <v>0.4337763956832553</v>
       </c>
       <c r="H10" t="n">
-        <v>66.56304695207569</v>
+        <v>59.74805885725614</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3752769754603133</v>
+        <v>0.3772056974762131</v>
       </c>
       <c r="J10" t="n">
-        <v>-76.62814356511547</v>
+        <v>-80.20441825691869</v>
       </c>
       <c r="K10" t="n">
-        <v>-62.70525523916555</v>
+        <v>-70.25949802409731</v>
       </c>
     </row>
     <row r="11">
@@ -843,36 +843,36 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>t_ind_ad, I, V_calc</t>
+          <t>t_ind_ad, I, X_calc, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.07647638699522741</v>
+        <v>0.1822671271866396</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2612040064190496</v>
+        <v>0.2454719392499524</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2145401277877305</v>
+        <v>0.1899642982151878</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4631847663597438</v>
+        <v>0.4358489396742727</v>
       </c>
       <c r="H11" t="n">
-        <v>80.93337502687031</v>
+        <v>72.74423551301183</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4287351733528431</v>
+        <v>0.3807948705946396</v>
       </c>
       <c r="J11" t="n">
-        <v>-77.11995803756395</v>
+        <v>-79.68963294485546</v>
       </c>
       <c r="K11" t="n">
-        <v>-71.15300589787113</v>
+        <v>-69.74471271203409</v>
       </c>
     </row>
     <row r="12">
